--- a/Donnees/Statisiques Environnementales et de la  gouvernace/Environnement/Theme_Environnement.xlsx
+++ b/Donnees/Statisiques Environnementales et de la  gouvernace/Environnement/Theme_Environnement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statisiques Environnementales et de la  gouvernace\Environnement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BCF62F-11FE-457C-ACD2-B03B049A3E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627BD9B-2F48-4FA3-946F-B25E0C2ADECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T4.30" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
-  <si>
-    <t>Tableau 3.1.1 : Nombre annuel des incendies et feux de brousse enregistrés durant la période  2008-2024</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
   <si>
     <t>2024</t>
   </si>
@@ -85,9 +82,6 @@
     <t>Source : MEDD/2008-2024</t>
   </si>
   <si>
-    <t>Tableau 3.1.2 : Superficies annuellement brulées par les incendies et feux de brousse durant la période 2008-2024</t>
-  </si>
-  <si>
     <t>Superficies (km²) ~2012</t>
   </si>
   <si>
@@ -139,30 +133,9 @@
     <t>Superficies (km²) ~2015</t>
   </si>
   <si>
-    <t>Tableau 3.1.3: Quantité  (en tonnes) de charbon transportée de l'intérieur vers Nouakchott  durant la période 2010-2019</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
     <t>Source : MEDD/2010-2019</t>
   </si>
   <si>
-    <t>Tableau 3.1.4: L'évolution de la proportion(en %) des ménages qui ont adopté des énergies alternatives propres telles que le gaz butane dans leurs cuissons durant la période  2004-2019</t>
-  </si>
-  <si>
-    <t>Années~2019</t>
-  </si>
-  <si>
-    <t>Années~2014</t>
-  </si>
-  <si>
-    <t>Années~2008</t>
-  </si>
-  <si>
-    <t>Années~2004</t>
-  </si>
-  <si>
     <t>Source : EPCV/2004-2019</t>
   </si>
   <si>
@@ -203,6 +176,18 @@
   </si>
   <si>
     <t>Wilaya~Nouakchott</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.2 : Superficies annuellement brulées par les incendies et feux de brousse  2008-2024</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.3: Quantité  (en tonnes) de charbon transportée de l'intérieur vers Nouakchott   2010-2019</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.1 : Nombre annuel des incendies et feux de brousse enregistrés  2008-2024</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.4: L'évolution de la proportion (en %) des ménages qui ont adopté des énergies alternatives propres telles que le gaz butane dans leurs cuissons   2004-2019</t>
   </si>
 </sst>
 </file>
@@ -565,66 +550,66 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>248</v>
@@ -680,7 +665,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>55</v>
@@ -736,7 +721,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>42</v>
@@ -792,7 +777,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>19</v>
@@ -848,7 +833,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>75</v>
@@ -904,7 +889,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>39</v>
@@ -960,7 +945,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>17</v>
@@ -1016,7 +1001,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1072,7 +1057,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1087,66 +1072,66 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>2436.3000000000002</v>
@@ -1202,7 +1187,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>1001</v>
@@ -1258,7 +1243,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>658.2</v>
@@ -1314,7 +1299,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>278.10000000000002</v>
@@ -1370,7 +1355,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>139.5</v>
@@ -1426,7 +1411,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>160.4</v>
@@ -1482,7 +1467,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>106.9</v>
@@ -1538,7 +1523,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>92</v>
@@ -1594,7 +1579,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1609,47 +1594,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>62992</v>
@@ -1684,7 +1667,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1702,27 +1685,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>45</v>
+      <c r="B2" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2014</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2008</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2004</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>46.719000000000001</v>
@@ -1739,7 +1722,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>25.3294</v>
@@ -1756,7 +1739,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>20.0367</v>
@@ -1773,7 +1756,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>32.273299999999999</v>
@@ -1790,7 +1773,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>4.3489000000000004</v>
@@ -1807,7 +1790,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>23.241099999999999</v>
@@ -1824,7 +1807,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>70.778700000000001</v>
@@ -1841,7 +1824,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>67.632499999999993</v>
@@ -1858,7 +1841,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>98.688800000000001</v>
@@ -1875,7 +1858,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>28.146799999999999</v>
@@ -1892,7 +1875,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>2.9256000000000002</v>
@@ -1909,7 +1892,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>73.047700000000006</v>
@@ -1926,7 +1909,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>95.354799999999997</v>
@@ -1943,7 +1926,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>87.0822</v>
@@ -1960,7 +1943,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
